--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>67180.22</v>
+        <v>127180.22</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-42323.54</v>
+        <v>-80123.53999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24856.68</v>
+        <v>47056.68</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>6224535.49</v>
+        <v>6284535.49</v>
       </c>
     </row>
     <row r="41">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-2894465.03</v>
+        <v>-2932265.03</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3330070.46</v>
+        <v>3352270.46</v>
       </c>
     </row>
     <row r="43">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="289">
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>-0</v>
+        <v>-18900</v>
       </c>
     </row>
     <row r="290">
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>0</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="291">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>2456502.71</v>
+        <v>2486502.71</v>
       </c>
     </row>
     <row r="292">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>-713853.33</v>
+        <v>-732753.33</v>
       </c>
     </row>
     <row r="293">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>1742649.38</v>
+        <v>1753749.38</v>
       </c>
     </row>
     <row r="294">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>1742649.38</v>
+        <v>1753749.38</v>
       </c>
     </row>
     <row r="295">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>4015041.7</v>
+        <v>4114791.7</v>
       </c>
     </row>
     <row r="299">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>1424309.39</v>
+        <v>1524059.39</v>
       </c>
     </row>
     <row r="301">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>4015041.7</v>
+        <v>4114791.7</v>
       </c>
     </row>
     <row r="311">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>1424309.39</v>
+        <v>1524059.39</v>
       </c>
     </row>
     <row r="313">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>1424309.39</v>
+        <v>1524059.39</v>
       </c>
     </row>
     <row r="314">
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>0</v>
+        <v>292500</v>
       </c>
     </row>
     <row r="369">
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>-0</v>
+        <v>-184275</v>
       </c>
     </row>
     <row r="370">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>0</v>
+        <v>108225</v>
       </c>
     </row>
     <row r="371">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>3685754.45</v>
+        <v>3978254.45</v>
       </c>
     </row>
     <row r="372">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>-2144384.8</v>
+        <v>-2328659.8</v>
       </c>
     </row>
     <row r="373">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>1541369.65</v>
+        <v>1649594.65</v>
       </c>
     </row>
     <row r="374">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>1541369.65</v>
+        <v>1649594.65</v>
       </c>
     </row>
     <row r="375">
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>1904136.13</v>
+        <v>2048400.13</v>
       </c>
     </row>
     <row r="388">
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>-1199605.76</v>
+        <v>-1290492.08</v>
       </c>
     </row>
     <row r="389">
@@ -10160,7 +10160,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>704530.37</v>
+        <v>757908.05</v>
       </c>
     </row>
     <row r="390">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>11536823.97</v>
+        <v>11681087.97</v>
       </c>
     </row>
     <row r="391">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>-6931058.52</v>
+        <v>-7021944.84</v>
       </c>
     </row>
     <row r="392">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>4605765.45</v>
+        <v>4659143.13</v>
       </c>
     </row>
     <row r="393">
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>215580.48</v>
+        <v>359844.48</v>
       </c>
     </row>
     <row r="411">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-32451.8</v>
+        <v>-123338.12</v>
       </c>
     </row>
     <row r="412">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>183128.68</v>
+        <v>236506.36</v>
       </c>
     </row>
     <row r="413">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>4760893.7</v>
+        <v>4905157.7</v>
       </c>
     </row>
     <row r="414">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-3086440.63</v>
+        <v>-3177326.95</v>
       </c>
     </row>
     <row r="415">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>1674453.07</v>
+        <v>1727830.75</v>
       </c>
     </row>
     <row r="416">
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>1674453.07</v>
+        <v>1727830.75</v>
       </c>
     </row>
     <row r="417">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>0</v>
+        <v>684750</v>
       </c>
     </row>
     <row r="468">
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>-0</v>
+        <v>-431392.5</v>
       </c>
     </row>
     <row r="469">
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>0</v>
+        <v>253357.5</v>
       </c>
     </row>
     <row r="470">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>13825143.05</v>
+        <v>14509893.05</v>
       </c>
     </row>
     <row r="471">
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>-8779281.42</v>
+        <v>-9210673.92</v>
       </c>
     </row>
     <row r="472">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>5045861.63</v>
+        <v>5299219.13</v>
       </c>
     </row>
     <row r="473">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>-1426517.06</v>
+        <v>-1469800.85</v>
       </c>
     </row>
     <row r="148">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>1215122.15</v>
+        <v>1171838.36</v>
       </c>
     </row>
     <row r="149">
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>-1426517.06</v>
+        <v>-1469800.85</v>
       </c>
     </row>
     <row r="160">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>1215122.15</v>
+        <v>1171838.36</v>
       </c>
     </row>
     <row r="161">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>1215122.15</v>
+        <v>1171838.36</v>
       </c>
     </row>
     <row r="162">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-1430318.25</v>
+        <v>-1658307.05</v>
       </c>
     </row>
     <row r="167">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>707099.0699999999</v>
+        <v>479110.27</v>
       </c>
     </row>
     <row r="168">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>-1430318.25</v>
+        <v>-1658307.05</v>
       </c>
     </row>
     <row r="179">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>707099.0699999999</v>
+        <v>479110.27</v>
       </c>
     </row>
     <row r="180">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>707099.0699999999</v>
+        <v>479110.27</v>
       </c>
     </row>
     <row r="181">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>-713853.33</v>
+        <v>-938367.77</v>
       </c>
     </row>
     <row r="281">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>1137790.48</v>
+        <v>913276.04</v>
       </c>
     </row>
     <row r="282">
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>-0</v>
+        <v>-578969.26</v>
       </c>
     </row>
     <row r="284">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>604858.9</v>
+        <v>25889.64</v>
       </c>
     </row>
     <row r="285">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>-732753.33</v>
+        <v>-1536237.03</v>
       </c>
     </row>
     <row r="293">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>1753749.38</v>
+        <v>950265.6800000001</v>
       </c>
     </row>
     <row r="294">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>1753749.38</v>
+        <v>950265.6800000001</v>
       </c>
     </row>
     <row r="295">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>-2590732.31</v>
+        <v>-2690482.31</v>
       </c>
     </row>
     <row r="300">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>1524059.39</v>
+        <v>1424309.39</v>
       </c>
     </row>
     <row r="301">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>-2590732.31</v>
+        <v>-2690482.31</v>
       </c>
     </row>
     <row r="312">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>1524059.39</v>
+        <v>1424309.39</v>
       </c>
     </row>
     <row r="313">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>1524059.39</v>
+        <v>1424309.39</v>
       </c>
     </row>
     <row r="314">
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>-2144384.8</v>
+        <v>-2126242.57</v>
       </c>
     </row>
     <row r="361">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>1541369.65</v>
+        <v>1559511.88</v>
       </c>
     </row>
     <row r="362">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>-2328659.8</v>
+        <v>-2310517.57</v>
       </c>
     </row>
     <row r="373">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>1649594.65</v>
+        <v>1667736.88</v>
       </c>
     </row>
     <row r="374">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>1649594.65</v>
+        <v>1667736.88</v>
       </c>
     </row>
     <row r="375">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-123338.12</v>
+        <v>-245290.26</v>
       </c>
     </row>
     <row r="412">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>236506.36</v>
+        <v>114554.22</v>
       </c>
     </row>
     <row r="413">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-3177326.95</v>
+        <v>-3299279.09</v>
       </c>
     </row>
     <row r="415">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>1727830.75</v>
+        <v>1605878.61</v>
       </c>
     </row>
     <row r="416">
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>1727830.75</v>
+        <v>1605878.61</v>
       </c>
     </row>
     <row r="417">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>-2191516.17</v>
+        <v>-2256181.96</v>
       </c>
     </row>
     <row r="441">
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>1767594.02</v>
+        <v>1702928.23</v>
       </c>
     </row>
     <row r="442">
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>-28825.46</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="444">
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>16462.54</v>
+        <v>45288</v>
       </c>
     </row>
     <row r="445">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>-86062.98</v>
+        <v>-189217.89</v>
       </c>
     </row>
     <row r="447">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>303405.22</v>
+        <v>200250.31</v>
       </c>
     </row>
     <row r="448">
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>-368075.03</v>
+        <v>-176533.75</v>
       </c>
     </row>
     <row r="450">
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>1105119.47</v>
+        <v>1296660.75</v>
       </c>
     </row>
     <row r="451">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-2674479.64</v>
+        <v>-2773533.22</v>
       </c>
     </row>
     <row r="453">
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>3192581.25</v>
+        <v>3093527.67</v>
       </c>
     </row>
     <row r="454">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>3192581.25</v>
+        <v>3093527.67</v>
       </c>
     </row>
     <row r="455">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>-5448861.23</v>
+        <v>-5557177.06</v>
       </c>
     </row>
     <row r="380">
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>3749070.41</v>
+        <v>3640754.58</v>
       </c>
     </row>
     <row r="381">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>-7021944.84</v>
+        <v>-7130260.67</v>
       </c>
     </row>
     <row r="392">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>4659143.13</v>
+        <v>4550827.3</v>
       </c>
     </row>
     <row r="393">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-245290.26</v>
+        <v>-103986.24</v>
       </c>
     </row>
     <row r="412">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>114554.22</v>
+        <v>255858.24</v>
       </c>
     </row>
     <row r="413">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-3299279.09</v>
+        <v>-3157975.07</v>
       </c>
     </row>
     <row r="415">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>1605878.61</v>
+        <v>1747182.63</v>
       </c>
     </row>
     <row r="416">
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>1605878.61</v>
+        <v>1747182.63</v>
       </c>
     </row>
     <row r="417">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>-2256181.96</v>
+        <v>-2364497.79</v>
       </c>
     </row>
     <row r="441">
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>1702928.23</v>
+        <v>1594612.4</v>
       </c>
     </row>
     <row r="442">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-2773533.22</v>
+        <v>-2838565.26</v>
       </c>
     </row>
     <row r="453">
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>3093527.67</v>
+        <v>3028495.63</v>
       </c>
     </row>
     <row r="454">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>3093527.67</v>
+        <v>3028495.63</v>
       </c>
     </row>
     <row r="455">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E477"/>
+  <dimension ref="A1:E458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2066,7 +2066,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CS Finance</t>
+          <t>CS Grupo Mult</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
@@ -2131,11 +2131,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
@@ -2281,11 +2281,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
@@ -2356,11 +2356,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
@@ -2431,11 +2431,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CS Grupo Mult</t>
+          <t>CS Health</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -2541,7 +2541,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CS Grupo Mult</t>
+          <t>CS Health</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -2601,16 +2601,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
@@ -2676,16 +2676,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -2751,16 +2751,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
@@ -2826,16 +2826,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
@@ -2901,16 +2901,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
@@ -2966,7 +2966,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CS Health</t>
+          <t>CS Multisector</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2976,22 +2976,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CS Health</t>
+          <t>CS Multisector</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
@@ -3016,7 +3016,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CS Health</t>
+          <t>CS Multisector</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3416,7 +3416,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CS Multisector</t>
+          <t>CS Retail</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3441,7 +3441,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CS Multisector</t>
+          <t>CS Retail</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CS Multisector</t>
+          <t>CS Retail</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CS Multisector</t>
+          <t>CS Retail</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
@@ -3551,16 +3551,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
@@ -3626,16 +3626,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
@@ -3701,16 +3701,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
@@ -3776,16 +3776,16 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
@@ -3851,37 +3851,37 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CS Retail</t>
+          <t>DANILO DE SOUZA MACIEIRA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
@@ -3891,22 +3891,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CS Retail</t>
+          <t>DANILO DE SOUZA MACIEIRA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E139" s="2" t="n">
@@ -3916,76 +3916,76 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CS Retail</t>
+          <t>DANILO DE SOUZA MACIEIRA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CS Retail</t>
+          <t>DANILO DE SOUZA MACIEIRA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0</v>
+        <v>2641639.21</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CS Retail</t>
+          <t>DANILO DE SOUZA MACIEIRA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0</v>
+        <v>-1426517.06</v>
       </c>
     </row>
     <row r="143">
@@ -4001,16 +4001,16 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0</v>
+        <v>1171838.36</v>
       </c>
     </row>
     <row r="144">
@@ -4026,16 +4026,16 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E145" s="2" t="n">
@@ -4076,16 +4076,16 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>2641639.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -4101,16 +4101,16 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>-1469800.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -4126,16 +4126,16 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>1171838.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
@@ -4176,16 +4176,16 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E151" s="2" t="n">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E152" s="2" t="n">
@@ -4251,16 +4251,16 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>-0</v>
+        <v>2641639.21</v>
       </c>
     </row>
     <row r="154">
@@ -4276,16 +4276,16 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0</v>
+        <v>-1426517.06</v>
       </c>
     </row>
     <row r="155">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0</v>
+        <v>1171838.36</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4326,22 +4326,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E157" s="2" t="n">
@@ -4366,7 +4366,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4376,22 +4376,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>2641639.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4401,22 +4401,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>-1469800.85</v>
+        <v>2137417.32</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>1171838.36</v>
+        <v>-1430318.25</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DANILO DE SOUZA MACIEIRA</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4451,16 +4451,16 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>1171838.36</v>
+        <v>479110.27</v>
       </c>
     </row>
     <row r="162">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>2137417.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>-1658307.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>479110.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0</v>
+        <v>2137417.32</v>
       </c>
     </row>
     <row r="172">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>-0</v>
+        <v>-1430318.25</v>
       </c>
     </row>
     <row r="173">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4760,23 +4760,23 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0</v>
+        <v>479110.27</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4791,17 +4791,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4810,23 +4810,23 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4841,17 +4841,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4860,23 +4860,23 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>2137417.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4885,23 +4885,23 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>-1658307.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4910,32 +4910,32 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>479110.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Estrategista Finance</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>ESTRATEGISTAS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>479110.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E181" s="2" t="n">
@@ -4976,16 +4976,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E183" s="2" t="n">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E184" s="2" t="n">
@@ -5051,16 +5051,16 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E186" s="2" t="n">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E187" s="2" t="n">
@@ -5126,16 +5126,16 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E189" s="2" t="n">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E190" s="2" t="n">
@@ -5201,22 +5201,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E192" s="2" t="n">
@@ -5241,7 +5241,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E193" s="2" t="n">
@@ -5266,7 +5266,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5276,22 +5276,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E195" s="2" t="n">
@@ -5316,7 +5316,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E196" s="2" t="n">
@@ -5341,7 +5341,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5351,22 +5351,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E198" s="2" t="n">
@@ -5391,7 +5391,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Estrategista Finance</t>
+          <t>Estrategista Grupo Mult</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E199" s="2" t="n">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E200" s="2" t="n">
@@ -5451,16 +5451,16 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E202" s="2" t="n">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E203" s="2" t="n">
@@ -5526,16 +5526,16 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E205" s="2" t="n">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E206" s="2" t="n">
@@ -5601,16 +5601,16 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E208" s="2" t="n">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E209" s="2" t="n">
@@ -5666,7 +5666,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5676,22 +5676,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E211" s="2" t="n">
@@ -5716,7 +5716,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E212" s="2" t="n">
@@ -5741,7 +5741,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5751,22 +5751,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E214" s="2" t="n">
@@ -5791,7 +5791,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E215" s="2" t="n">
@@ -5816,7 +5816,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E217" s="2" t="n">
@@ -5866,7 +5866,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Estrategista Grupo Mult</t>
+          <t>Estrategista Health</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E218" s="2" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6141,7 +6141,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6160,13 +6160,13 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6191,7 +6191,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6266,7 +6266,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6310,13 +6310,13 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6341,7 +6341,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Estrategista Health</t>
+          <t>Estrategista Multisector</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E237" s="2" t="n">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E238" s="2" t="n">
@@ -6401,16 +6401,16 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E240" s="2" t="n">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E241" s="2" t="n">
@@ -6476,16 +6476,16 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -6501,12 +6501,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E243" s="2" t="n">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E244" s="2" t="n">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E246" s="2" t="n">
@@ -6591,7 +6591,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E247" s="2" t="n">
@@ -6616,7 +6616,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E249" s="2" t="n">
@@ -6666,7 +6666,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E250" s="2" t="n">
@@ -6691,7 +6691,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6701,22 +6701,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E252" s="2" t="n">
@@ -6741,7 +6741,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E253" s="2" t="n">
@@ -6766,7 +6766,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6776,22 +6776,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E255" s="2" t="n">
@@ -6816,7 +6816,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Estrategista Multisector</t>
+          <t>Estrategista Retail</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E256" s="2" t="n">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E257" s="2" t="n">
@@ -6876,16 +6876,16 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E259" s="2" t="n">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E260" s="2" t="n">
@@ -6951,16 +6951,16 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E262" s="2" t="n">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E263" s="2" t="n">
@@ -7016,47 +7016,47 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E265" s="2" t="n">
@@ -7066,22 +7066,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E266" s="2" t="n">
@@ -7091,122 +7091,122 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>-0</v>
+        <v>1851643.81</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0</v>
+        <v>-713853.33</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0</v>
+        <v>913276.04</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>-0</v>
+        <v>604858.9</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E271" s="2" t="n">
@@ -7216,72 +7216,72 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0</v>
+        <v>25889.64</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E274" s="2" t="n">
@@ -7291,22 +7291,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Estrategista Retail</t>
+          <t>FABIO LUIS BERTI BARCELOS</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ESTRATEGISTAS</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E275" s="2" t="n">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="277">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>-0</v>
+        <v>-18900</v>
       </c>
     </row>
     <row r="278">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="279">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>1851643.81</v>
+        <v>2486502.71</v>
       </c>
     </row>
     <row r="280">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>-938367.77</v>
+        <v>-732753.33</v>
       </c>
     </row>
     <row r="281">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>913276.04</v>
+        <v>950265.6800000001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7485,13 +7485,13 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>604858.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7510,13 +7510,13 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>-578969.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7535,13 +7535,13 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>25889.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7560,13 +7560,13 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0</v>
+        <v>4114791.7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7585,13 +7585,13 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>-0</v>
+        <v>-2590732.31</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -7610,13 +7610,13 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0</v>
+        <v>1424309.39</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>-18900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7685,13 +7685,13 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>11100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>2486502.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7735,13 +7735,13 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>-1536237.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7760,13 +7760,13 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>950265.6800000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FABIO LUIS BERTI BARCELOS</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7776,16 +7776,16 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>950265.6800000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E295" s="2" t="n">
@@ -7826,16 +7826,16 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -7851,16 +7851,16 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0</v>
+        <v>4114791.7</v>
       </c>
     </row>
     <row r="298">
@@ -7876,16 +7876,16 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>4114791.7</v>
+        <v>-2590732.31</v>
       </c>
     </row>
     <row r="299">
@@ -7901,187 +7901,187 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>-2690482.31</v>
+        <v>1424309.39</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>1424309.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0</v>
+        <v>11126186.43</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0</v>
+        <v>-6619865.57</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>-0</v>
+        <v>4506320.86</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E306" s="2" t="n">
@@ -8091,72 +8091,72 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E309" s="2" t="n">
@@ -8166,101 +8166,101 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>4114791.7</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>-2690482.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>1424309.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>1424309.39</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="314">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E314" s="2" t="n">
@@ -8301,16 +8301,16 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>-0</v>
+        <v>11126186.43</v>
       </c>
     </row>
     <row r="316">
@@ -8326,16 +8326,16 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0</v>
+        <v>-6619865.57</v>
       </c>
     </row>
     <row r="317">
@@ -8351,16 +8351,16 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>11126186.43</v>
+        <v>4506320.86</v>
       </c>
     </row>
     <row r="318">
@@ -8376,16 +8376,16 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>-6619865.57</v>
+        <v>13728857.99</v>
       </c>
     </row>
     <row r="319">
@@ -8401,16 +8401,16 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>4506320.86</v>
+        <v>-5566531.04</v>
       </c>
     </row>
     <row r="320">
@@ -8426,16 +8426,16 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0</v>
+        <v>8162326.95</v>
       </c>
     </row>
     <row r="321">
@@ -8451,16 +8451,16 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>-0</v>
+        <v>-975519.47</v>
       </c>
     </row>
     <row r="322">
@@ -8476,32 +8476,32 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>0</v>
+        <v>7186807.48</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8516,17 +8516,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8535,23 +8535,23 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8566,17 +8566,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8585,23 +8585,23 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0</v>
+        <v>2458912.71</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8610,23 +8610,23 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>-0</v>
+        <v>-1349591.15</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8635,23 +8635,23 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0</v>
+        <v>1109321.56</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -8660,23 +8660,23 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>11126186.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8685,23 +8685,23 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>-6619865.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -8710,23 +8710,23 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>4506320.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8735,23 +8735,23 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>13728857.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8760,82 +8760,82 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>-5566531.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>8162326.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>-975519.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>7186807.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E337" s="2" t="n">
@@ -8876,16 +8876,16 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>-0</v>
+        <v>2458912.71</v>
       </c>
     </row>
     <row r="339">
@@ -8901,16 +8901,16 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>0</v>
+        <v>-1349591.15</v>
       </c>
     </row>
     <row r="340">
@@ -8926,22 +8926,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>2458912.71</v>
+        <v>1109321.56</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>-1349591.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>1109321.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E343" s="2" t="n">
@@ -9016,7 +9016,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9026,22 +9026,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>-0</v>
+        <v>3685754.45</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9051,22 +9051,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>0</v>
+        <v>-2144384.8</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9076,22 +9076,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>0</v>
+        <v>1559511.88</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9101,22 +9101,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E348" s="2" t="n">
@@ -9141,7 +9141,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E349" s="2" t="n">
@@ -9166,7 +9166,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9176,22 +9176,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E351" s="2" t="n">
@@ -9216,7 +9216,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9226,22 +9226,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>2458912.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9251,22 +9251,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>-1349591.15</v>
+        <v>292500</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>1109321.56</v>
+        <v>-184275</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO DOS SANTOS GARCIA</t>
+          <t>MIRELLA ANDRADE ARAUJO</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -9301,16 +9301,16 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>1109321.56</v>
+        <v>108225</v>
       </c>
     </row>
     <row r="356">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>0</v>
+        <v>3978254.45</v>
       </c>
     </row>
     <row r="357">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>-0</v>
+        <v>-2328659.8</v>
       </c>
     </row>
     <row r="358">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -9385,23 +9385,23 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>0</v>
+        <v>1667736.88</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9410,23 +9410,23 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>3685754.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9435,23 +9435,23 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>-2126242.57</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9460,23 +9460,23 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>1559511.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9485,23 +9485,23 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>0</v>
+        <v>9197931.640000001</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9510,23 +9510,23 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>-0</v>
+        <v>-5557177.06</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9535,23 +9535,23 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>0</v>
+        <v>3640754.58</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -9560,23 +9560,23 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>0</v>
+        <v>45288</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9585,23 +9585,23 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>-0</v>
+        <v>-29437.2</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9610,23 +9610,23 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>0</v>
+        <v>15850.8</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9635,23 +9635,23 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>292500</v>
+        <v>389468.2</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9660,23 +9660,23 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>-184275</v>
+        <v>-253154.33</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9685,23 +9685,23 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>108225</v>
+        <v>136313.87</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9710,23 +9710,23 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>3978254.45</v>
+        <v>2048400.13</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -9735,23 +9735,23 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>-2310517.57</v>
+        <v>-1290492.08</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9760,18 +9760,18 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>1667736.88</v>
+        <v>757908.05</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>MIRELLA ANDRADE ARAUJO</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -9781,11 +9781,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>1667736.88</v>
+        <v>11681087.97</v>
       </c>
     </row>
     <row r="375">
@@ -9801,16 +9801,16 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>0</v>
+        <v>-7130260.67</v>
       </c>
     </row>
     <row r="376">
@@ -9826,16 +9826,16 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>-0</v>
+        <v>4550827.3</v>
       </c>
     </row>
     <row r="377">
@@ -9851,16 +9851,16 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>0</v>
+        <v>13163491.45</v>
       </c>
     </row>
     <row r="378">
@@ -9876,16 +9876,16 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>9197931.640000001</v>
+        <v>-6308226.21</v>
       </c>
     </row>
     <row r="379">
@@ -9901,16 +9901,16 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>-5557177.06</v>
+        <v>6855265.24</v>
       </c>
     </row>
     <row r="380">
@@ -9926,16 +9926,16 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>3640754.58</v>
+        <v>-1398244.81</v>
       </c>
     </row>
     <row r="381">
@@ -9951,416 +9951,416 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>45288</v>
+        <v>5457020.43</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>-29437.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>15850.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>389468.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>-253154.33</v>
+        <v>4545313.22</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>136313.87</v>
+        <v>-3053988.83</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>2048400.13</v>
+        <v>1491324.39</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>-1290492.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>757908.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>11681087.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>-7130260.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>4550827.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>13163491.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>-6308226.21</v>
+        <v>359844.48</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>6855265.24</v>
+        <v>-123338.12</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>-1398244.81</v>
+        <v>255858.24</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Nicolly Brasil</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DIRETOR</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>NEXUS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>5457020.43</v>
+        <v>4905157.7</v>
       </c>
     </row>
     <row r="398">
@@ -10376,16 +10376,16 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>0</v>
+        <v>-3177326.95</v>
       </c>
     </row>
     <row r="399">
@@ -10401,22 +10401,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>-0</v>
+        <v>1747182.63</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E400" s="2" t="n">
@@ -10441,7 +10441,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -10451,22 +10451,22 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>4545313.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -10476,22 +10476,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>-3053988.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -10506,17 +10506,17 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>1491324.39</v>
+        <v>6380129.64</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -10526,22 +10526,22 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>0</v>
+        <v>-4338536.69</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>-0</v>
+        <v>2041592.95</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E406" s="2" t="n">
@@ -10591,7 +10591,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E407" s="2" t="n">
@@ -10616,7 +10616,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -10626,22 +10626,22 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E409" s="2" t="n">
@@ -10666,7 +10666,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -10676,22 +10676,22 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>359844.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -10701,22 +10701,22 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>-103986.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -10731,17 +10731,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>255858.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -10751,22 +10751,22 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>4905157.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -10776,22 +10776,22 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>-3157975.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -10806,17 +10806,17 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>1747182.63</v>
+        <v>6380129.64</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Nicolly Brasil</t>
+          <t>RICARDO SALLES HENRIQUE</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -10831,11 +10831,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>1747182.63</v>
+        <v>-4338536.69</v>
       </c>
     </row>
     <row r="417">
@@ -10851,22 +10851,22 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>0</v>
+        <v>2041592.95</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10881,17 +10881,17 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E419" s="2" t="n">
@@ -10916,7 +10916,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10926,22 +10926,22 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>CLOUD</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>6380129.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10956,17 +10956,17 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>-4338536.69</v>
+        <v>3959110.19</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10981,17 +10981,17 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>2041592.95</v>
+        <v>-2364497.79</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11001,22 +11001,22 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DADOS</t>
+          <t>APPS</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>0</v>
+        <v>1594612.4</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11031,17 +11031,17 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>-0</v>
+        <v>45288</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E425" s="2" t="n">
@@ -11066,7 +11066,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -11076,22 +11076,22 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>HYPER</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>0</v>
+        <v>45288</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11106,17 +11106,17 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>-0</v>
+        <v>389468.2</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11131,17 +11131,17 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>0</v>
+        <v>-189217.89</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -11151,22 +11151,22 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DEMAIS</t>
+          <t>HYPER</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>0</v>
+        <v>200250.31</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -11181,17 +11181,17 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>-0</v>
+        <v>1473194.5</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11206,17 +11206,17 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>0</v>
+        <v>-120763.96</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -11226,22 +11226,22 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>DEMAIS</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>6380129.64</v>
+        <v>1296660.75</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -11256,17 +11256,17 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>-4338536.69</v>
+        <v>5867060.89</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -11281,17 +11281,17 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>2041592.95</v>
+        <v>-2473314.55</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>RICARDO SALLES HENRIQUE</t>
+          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -11306,22 +11306,22 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>2041592.95</v>
+        <v>3028495.63</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -11341,12 +11341,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -11366,12 +11366,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -11391,12 +11391,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -11410,18 +11410,18 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>3959110.19</v>
+        <v>13825143.05</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -11435,18 +11435,18 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>-2364497.79</v>
+        <v>-8779281.42</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -11460,18 +11460,18 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>1594612.4</v>
+        <v>5045861.63</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -11485,18 +11485,18 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>45288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -11516,12 +11516,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -11535,18 +11535,18 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>45288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -11560,18 +11560,18 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>389468.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -11585,18 +11585,18 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>-189217.89</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -11610,18 +11610,18 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>200250.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -11635,18 +11635,18 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>1473194.5</v>
+        <v>684750</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -11660,18 +11660,18 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>-176533.75</v>
+        <v>-431392.5</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -11685,18 +11685,18 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>1296660.75</v>
+        <v>253357.5</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -11710,18 +11710,18 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>5867060.89</v>
+        <v>14509893.05</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -11735,18 +11735,18 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-2838565.26</v>
+        <v>-9210673.92</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -11760,32 +11760,32 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>3028495.63</v>
+        <v>5299219.13</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>VINICIUS TEDESCO GANDRA MARTINS</t>
+          <t>Zanini</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DIRETOR</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>Receita</t>
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>3028495.63</v>
+        <v>20960688.43</v>
       </c>
     </row>
     <row r="455">
@@ -11801,16 +11801,16 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>Custo</t>
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>0</v>
+        <v>-7545350.71</v>
       </c>
     </row>
     <row r="456">
@@ -11826,16 +11826,16 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Custo</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>-0</v>
+        <v>13415337.72</v>
       </c>
     </row>
     <row r="457">
@@ -11851,16 +11851,16 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>0</v>
+        <v>-2052011.59</v>
       </c>
     </row>
     <row r="458">
@@ -11876,490 +11876,15 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>APPS</t>
+          <t>NEXUS</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Receita</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>13825143.05</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>APPS</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E459" s="2" t="n">
-        <v>-8779281.42</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>APPS</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="n">
-        <v>5045861.63</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>DADOS</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="E461" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>DADOS</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E462" s="2" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>DADOS</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>HYPER</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="E464" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>HYPER</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E465" s="2" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>HYPER</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>DEMAIS</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="E467" s="2" t="n">
-        <v>684750</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>DEMAIS</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E468" s="2" t="n">
-        <v>-431392.5</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>DEMAIS</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E469" s="2" t="n">
-        <v>253357.5</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="n">
-        <v>14509893.05</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="n">
-        <v>-9210673.92</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E472" s="2" t="n">
-        <v>5299219.13</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>NEXUS</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>Receita</t>
-        </is>
-      </c>
-      <c r="E473" s="2" t="n">
-        <v>20960688.43</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>NEXUS</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>Custo</t>
-        </is>
-      </c>
-      <c r="E474" s="2" t="n">
-        <v>-7545350.71</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>NEXUS</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="E475" s="2" t="n">
-        <v>13415337.72</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>NEXUS</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="E476" s="2" t="n">
-        <v>-2052011.59</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Zanini</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>DIRETOR</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>NEXUS</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="E477" s="2" t="n">
         <v>11363326.13</v>
       </c>
     </row>

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>604858.9</v>
+        <v>572779.74</v>
       </c>
     </row>
     <row r="271">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>2486502.71</v>
+        <v>2454423.55</v>
       </c>
     </row>
     <row r="280">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>389468.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>-189217.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>200250.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>5867060.89</v>
+        <v>5477592.69</v>
       </c>
     </row>
     <row r="434">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>-2473314.55</v>
+        <v>-2284096.66</v>
       </c>
     </row>
     <row r="435">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>3028495.63</v>
+        <v>2828245.32</v>
       </c>
     </row>
     <row r="436">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0</v>
+        <v>-16828.27</v>
       </c>
     </row>
     <row r="272">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>25889.64</v>
+        <v>9061.370000000001</v>
       </c>
     </row>
     <row r="273">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>-732753.33</v>
+        <v>-749581.6</v>
       </c>
     </row>
     <row r="281">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>950265.6800000001</v>
+        <v>933437.41</v>
       </c>
     </row>
     <row r="282">
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>-123338.12</v>
+        <v>-238893.71</v>
       </c>
     </row>
     <row r="396">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>255858.24</v>
+        <v>140302.65</v>
       </c>
     </row>
     <row r="397">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>-3177326.95</v>
+        <v>-3292882.54</v>
       </c>
     </row>
     <row r="399">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>1747182.63</v>
+        <v>1631627.04</v>
       </c>
     </row>
     <row r="400">
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>0</v>
+        <v>-29437.2</v>
       </c>
     </row>
     <row r="426">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>45288</v>
+        <v>15850.8</v>
       </c>
     </row>
     <row r="427">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>-120763.96</v>
+        <v>-914905.5699999999</v>
       </c>
     </row>
     <row r="432">
@@ -11235,7 +11235,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>1296660.75</v>
+        <v>502519.14</v>
       </c>
     </row>
     <row r="433">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>-2284096.66</v>
+        <v>-3107675.47</v>
       </c>
     </row>
     <row r="435">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>2828245.32</v>
+        <v>2004666.51</v>
       </c>
     </row>
     <row r="436">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>-16828.27</v>
+        <v>-372306.83</v>
       </c>
     </row>
     <row r="272">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>9061.370000000001</v>
+        <v>200472.91</v>
       </c>
     </row>
     <row r="273">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>-749581.6</v>
+        <v>-1105060.16</v>
       </c>
     </row>
     <row r="281">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>933437.41</v>
+        <v>1124848.95</v>
       </c>
     </row>
     <row r="282">
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>-238893.71</v>
+        <v>-226702.02</v>
       </c>
     </row>
     <row r="396">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>140302.65</v>
+        <v>133142.46</v>
       </c>
     </row>
     <row r="397">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>-3292882.54</v>
+        <v>-3280690.86</v>
       </c>
     </row>
     <row r="399">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>1631627.04</v>
+        <v>1624466.84</v>
       </c>
     </row>
     <row r="400">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>-914905.5699999999</v>
+        <v>-928112.54</v>
       </c>
     </row>
     <row r="432">
@@ -11235,7 +11235,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>502519.14</v>
+        <v>545081.96</v>
       </c>
     </row>
     <row r="433">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>-3107675.47</v>
+        <v>-3322047.53</v>
       </c>
     </row>
     <row r="435">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>2004666.51</v>
+        <v>2155545.16</v>
       </c>
     </row>
     <row r="436">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -433,7 +433,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5177271.64</v>
+        <v>12190846.81</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-3444306.98</v>
+        <v>-8914030.9</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1732964.66</v>
+        <v>3276815.91</v>
       </c>
     </row>
     <row r="8">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>578052.61</v>
+        <v>638826.13</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-375734.2</v>
+        <v>-415236.98</v>
       </c>
     </row>
     <row r="13">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>202318.41</v>
+        <v>223589.15</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1152892.68</v>
+        <v>2772052.34</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-726322.39</v>
+        <v>-1746392.97</v>
       </c>
     </row>
     <row r="16">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>426570.29</v>
+        <v>1025659.37</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6908216.93</v>
+        <v>15601725.28</v>
       </c>
     </row>
     <row r="18">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-4546363.57</v>
+        <v>-11075660.85</v>
       </c>
     </row>
     <row r="19">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2361853.36</v>
+        <v>4526064.43</v>
       </c>
     </row>
     <row r="20">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>188722.96</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0</v>
+        <v>-124557.15</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>64165.81</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5150089.72</v>
+        <v>5882054.79</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-2197418.88</v>
+        <v>-3184656.42</v>
       </c>
     </row>
     <row r="30">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2952670.84</v>
+        <v>2697398.37</v>
       </c>
     </row>
     <row r="31">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>604858.9</v>
+        <v>902579.42</v>
       </c>
     </row>
     <row r="32">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-393158.29</v>
+        <v>-586676.62</v>
       </c>
     </row>
     <row r="33">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>211700.61</v>
+        <v>315902.8</v>
       </c>
     </row>
     <row r="34">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>402406.65</v>
+        <v>403147.47</v>
       </c>
     </row>
     <row r="35">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-261564.32</v>
+        <v>-262045.86</v>
       </c>
     </row>
     <row r="36">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>140842.33</v>
+        <v>141101.61</v>
       </c>
     </row>
     <row r="37">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>127180.22</v>
+        <v>214987.32</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-80123.53999999999</v>
+        <v>-135442.01</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>47056.68</v>
+        <v>79545.31</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>6284535.49</v>
+        <v>7591491.96</v>
       </c>
     </row>
     <row r="41">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-2932265.03</v>
+        <v>-4293378.06</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3352270.46</v>
+        <v>3298113.9</v>
       </c>
     </row>
     <row r="43">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>-1426517.06</v>
+        <v>-1446757.06</v>
       </c>
     </row>
     <row r="143">
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>1171838.36</v>
+        <v>1151598.36</v>
       </c>
     </row>
     <row r="144">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>-1426517.06</v>
+        <v>-1446757.06</v>
       </c>
     </row>
     <row r="155">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>1171838.36</v>
+        <v>1151598.36</v>
       </c>
     </row>
     <row r="156">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>-1430318.25</v>
+        <v>-1681883.3</v>
       </c>
     </row>
     <row r="161">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>479110.27</v>
+        <v>227545.22</v>
       </c>
     </row>
     <row r="162">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>-1430318.25</v>
+        <v>-1681883.3</v>
       </c>
     </row>
     <row r="173">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>479110.27</v>
+        <v>227545.22</v>
       </c>
     </row>
     <row r="174">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0</v>
+        <v>166549.02</v>
       </c>
     </row>
     <row r="265">
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0</v>
+        <v>-109922.35</v>
       </c>
     </row>
     <row r="266">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0</v>
+        <v>56626.67</v>
       </c>
     </row>
     <row r="267">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>1851643.81</v>
+        <v>2180205.61</v>
       </c>
     </row>
     <row r="268">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>-713853.33</v>
+        <v>-650050.16</v>
       </c>
     </row>
     <row r="269">
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>913276.04</v>
+        <v>746305.74</v>
       </c>
     </row>
     <row r="270">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>572779.74</v>
+        <v>77668.92</v>
       </c>
     </row>
     <row r="271">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>-372306.83</v>
+        <v>-50484.8</v>
       </c>
     </row>
     <row r="272">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>200472.91</v>
+        <v>27184.12</v>
       </c>
     </row>
     <row r="273">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>-1105060.16</v>
+        <v>-829357.3100000001</v>
       </c>
     </row>
     <row r="281">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>1124848.95</v>
+        <v>841216.53</v>
       </c>
     </row>
     <row r="282">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>11126186.43</v>
+        <v>11539673.15</v>
       </c>
     </row>
     <row r="304">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>-6619865.57</v>
+        <v>-7425141.36</v>
       </c>
     </row>
     <row r="305">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>4506320.86</v>
+        <v>4114531.79</v>
       </c>
     </row>
     <row r="306">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0</v>
+        <v>62118.66</v>
       </c>
     </row>
     <row r="310">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>-0</v>
+        <v>-40377.13</v>
       </c>
     </row>
     <row r="311">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0</v>
+        <v>21741.53</v>
       </c>
     </row>
     <row r="312">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0</v>
+        <v>-188859.67</v>
       </c>
     </row>
     <row r="313">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>-0</v>
+        <v>188859.67</v>
       </c>
     </row>
     <row r="314">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>11126186.43</v>
+        <v>11412932.14</v>
       </c>
     </row>
     <row r="316">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>-6619865.57</v>
+        <v>-7276658.82</v>
       </c>
     </row>
     <row r="317">
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>4506320.86</v>
+        <v>4136273.32</v>
       </c>
     </row>
     <row r="318">
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>2458912.71</v>
+        <v>3822498.48</v>
       </c>
     </row>
     <row r="327">
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>-1349591.15</v>
+        <v>-1827759.16</v>
       </c>
     </row>
     <row r="328">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>1109321.56</v>
+        <v>2001739</v>
       </c>
     </row>
     <row r="329">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>0</v>
+        <v>440669.63</v>
       </c>
     </row>
     <row r="336">
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0</v>
+        <v>-277621.87</v>
       </c>
     </row>
     <row r="337">
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0</v>
+        <v>163047.76</v>
       </c>
     </row>
     <row r="338">
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>2458912.71</v>
+        <v>4263168.11</v>
       </c>
     </row>
     <row r="339">
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>-1349591.15</v>
+        <v>-2105381.03</v>
       </c>
     </row>
     <row r="340">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>1109321.56</v>
+        <v>2164786.77</v>
       </c>
     </row>
     <row r="341">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>-2144384.8</v>
+        <v>-2145446.18</v>
       </c>
     </row>
     <row r="346">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>1559511.88</v>
+        <v>1558450.5</v>
       </c>
     </row>
     <row r="347">
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>-2328659.8</v>
+        <v>-2329721.18</v>
       </c>
     </row>
     <row r="358">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>1667736.88</v>
+        <v>1666675.5</v>
       </c>
     </row>
     <row r="359">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>9197931.640000001</v>
+        <v>10179598.96</v>
       </c>
     </row>
     <row r="363">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>-5557177.06</v>
+        <v>-6005376.54</v>
       </c>
     </row>
     <row r="364">
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>3640754.58</v>
+        <v>4174222.42</v>
       </c>
     </row>
     <row r="365">
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>389468.2</v>
+        <v>426454.36</v>
       </c>
     </row>
     <row r="369">
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>-253154.33</v>
+        <v>-277195.33</v>
       </c>
     </row>
     <row r="370">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>136313.87</v>
+        <v>149259.03</v>
       </c>
     </row>
     <row r="371">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>2048400.13</v>
+        <v>2744820.5</v>
       </c>
     </row>
     <row r="372">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>-1290492.08</v>
+        <v>-1729236.92</v>
       </c>
     </row>
     <row r="373">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>757908.05</v>
+        <v>1015583.58</v>
       </c>
     </row>
     <row r="374">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>11681087.97</v>
+        <v>13396161.82</v>
       </c>
     </row>
     <row r="375">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>-7130260.67</v>
+        <v>-8041245.99</v>
       </c>
     </row>
     <row r="376">
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>4550827.3</v>
+        <v>5354915.83</v>
       </c>
     </row>
     <row r="377">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>-3053988.83</v>
+        <v>-3292940.41</v>
       </c>
     </row>
     <row r="387">
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>1491324.39</v>
+        <v>1252372.81</v>
       </c>
     </row>
     <row r="388">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>-3280690.86</v>
+        <v>-3519642.43</v>
       </c>
     </row>
     <row r="399">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>1624466.84</v>
+        <v>1385515.27</v>
       </c>
     </row>
     <row r="400">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>-2364497.79</v>
+        <v>-2401132.25</v>
       </c>
     </row>
     <row r="423">
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>1594612.4</v>
+        <v>1557977.94</v>
       </c>
     </row>
     <row r="424">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>-3322047.53</v>
+        <v>-3358681.99</v>
       </c>
     </row>
     <row r="435">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>2155545.16</v>
+        <v>2118910.7</v>
       </c>
     </row>
     <row r="436">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>13825143.05</v>
+        <v>16043084.54</v>
       </c>
     </row>
     <row r="440">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>-8779281.42</v>
+        <v>-9487141.949999999</v>
       </c>
     </row>
     <row r="441">
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>5045861.63</v>
+        <v>6555942.59</v>
       </c>
     </row>
     <row r="442">
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>0</v>
+        <v>387515.97</v>
       </c>
     </row>
     <row r="446">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>-0</v>
+        <v>-251885.38</v>
       </c>
     </row>
     <row r="447">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>0</v>
+        <v>135630.59</v>
       </c>
     </row>
     <row r="448">
@@ -11635,7 +11635,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>684750</v>
+        <v>809410.62</v>
       </c>
     </row>
     <row r="449">
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>-431392.5</v>
+        <v>-509928.69</v>
       </c>
     </row>
     <row r="450">
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>253357.5</v>
+        <v>299481.93</v>
       </c>
     </row>
     <row r="451">
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>14509893.05</v>
+        <v>17240011.13</v>
       </c>
     </row>
     <row r="452">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-9210673.92</v>
+        <v>-10248956.02</v>
       </c>
     </row>
     <row r="453">
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>5299219.13</v>
+        <v>6991055.109999999</v>
       </c>
     </row>
     <row r="454">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>188722.96</v>
+        <v>166549.02</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-124557.15</v>
+        <v>-109922.35</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>64165.81</v>
+        <v>56626.67</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5882054.79</v>
+        <v>5796717.21</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-3184656.42</v>
+        <v>-3099318.84</v>
       </c>
     </row>
     <row r="30">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>214987.32</v>
+        <v>322498.84</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-135442.01</v>
+        <v>-203174.27</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>79545.31</v>
+        <v>119324.57</v>
       </c>
     </row>
     <row r="40">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-4293378.06</v>
+        <v>-4261137.94</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>3298113.9</v>
+        <v>3330354.02</v>
       </c>
     </row>
     <row r="43">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>11539673.15</v>
+        <v>11350813.48</v>
       </c>
     </row>
     <row r="304">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>-7425141.36</v>
+        <v>-7236281.69</v>
       </c>
     </row>
     <row r="305">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>-188859.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>188859.67</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="314">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>10179598.96</v>
+        <v>10171510.54</v>
       </c>
     </row>
     <row r="363">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>-6005376.54</v>
+        <v>-5997288.12</v>
       </c>
     </row>
     <row r="364">
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>-277195.33</v>
+        <v>-288647.12</v>
       </c>
     </row>
     <row r="370">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>149259.03</v>
+        <v>137807.24</v>
       </c>
     </row>
     <row r="371">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>2744820.5</v>
+        <v>2752908.92</v>
       </c>
     </row>
     <row r="372">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>-1729236.92</v>
+        <v>-1756260.62</v>
       </c>
     </row>
     <row r="373">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>1015583.58</v>
+        <v>996648.3</v>
       </c>
     </row>
     <row r="374">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>-8041245.99</v>
+        <v>-8071633.06</v>
       </c>
     </row>
     <row r="376">
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>5354915.83</v>
+        <v>5324528.76</v>
       </c>
     </row>
     <row r="377">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>16043084.54</v>
+        <v>16026575.21</v>
       </c>
     </row>
     <row r="440">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>-9487141.949999999</v>
+        <v>-9470632.619999999</v>
       </c>
     </row>
     <row r="441">
@@ -11635,7 +11635,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>809410.62</v>
+        <v>825919.95</v>
       </c>
     </row>
     <row r="449">
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>-509928.69</v>
+        <v>-854886.62</v>
       </c>
     </row>
     <row r="450">
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>299481.93</v>
+        <v>-28966.67</v>
       </c>
     </row>
     <row r="451">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>-10248956.02</v>
+        <v>-10577404.62</v>
       </c>
     </row>
     <row r="453">
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>6991055.109999999</v>
+        <v>6662606.51</v>
       </c>
     </row>
     <row r="454">

--- a/backend/apuracao_q4_exportado.xlsx
+++ b/backend/apuracao_q4_exportado.xlsx
@@ -433,7 +433,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3758108.11</v>
+        <v>3678409.51</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7444</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29.01</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="12">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12190846.81</v>
+        <v>12105554.24</v>
       </c>
     </row>
     <row r="16">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-8914030.9</v>
+        <v>-8858626.9</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3276815.91</v>
+        <v>3246927.34</v>
       </c>
     </row>
     <row r="18">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>638826.13</v>
+        <v>73917.02</v>
       </c>
     </row>
     <row r="22">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-415236.98</v>
+        <v>-48046.06</v>
       </c>
     </row>
     <row r="23">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>223589.15</v>
+        <v>25870.96</v>
       </c>
     </row>
     <row r="24">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2772052.34</v>
+        <v>2819287.29</v>
       </c>
     </row>
     <row r="25">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-1746392.97</v>
+        <v>-1776150.99</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1025659.37</v>
+        <v>1043136.3</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15601725.28</v>
+        <v>14998758.55</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-11075660.85</v>
+        <v>-10682823.95</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>4526064.43</v>
+        <v>4315934.6</v>
       </c>
     </row>
     <row r="30">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2956681.62</v>
+        <v>2900236.83</v>
       </c>
     </row>
     <row r="43">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9069</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>43.87</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="45">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>403147.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>-262045.86</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="56">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>141101.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>322498.84</v>
+        <v>372961.84</v>
       </c>
     </row>
     <row r="58">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>-203174.27</v>
+        <v>-234965.96</v>
       </c>
     </row>
     <row r="59">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>119324.57</v>
+        <v>137995.88</v>
       </c>
     </row>
     <row r="60">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>7591491.96</v>
+        <v>7238807.49</v>
       </c>
     </row>
     <row r="61">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-4261137.94</v>
+        <v>-4030883.77</v>
       </c>
     </row>
     <row r="62">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3330354.02</v>
+        <v>3207923.72</v>
       </c>
     </row>
     <row r="63">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>4465112.66</v>
+        <v>5025921</v>
       </c>
     </row>
     <row r="201">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>2641639.21</v>
+        <v>2225236.72</v>
       </c>
     </row>
     <row r="202">
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>39.14</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="204">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>43.59</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="205">
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>1</v>
+        <v>0.8250999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>2641639.21</v>
+        <v>2225236.72</v>
       </c>
     </row>
     <row r="210">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>-1446757.06</v>
+        <v>-1401823.44</v>
       </c>
     </row>
     <row r="211">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>1151598.36</v>
+        <v>847421.75</v>
       </c>
     </row>
     <row r="212">
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>2641639.21</v>
+        <v>2225236.72</v>
       </c>
     </row>
     <row r="222">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>-1446757.06</v>
+        <v>-1401823.44</v>
       </c>
     </row>
     <row r="223">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>1151598.36</v>
+        <v>847421.75</v>
       </c>
     </row>
     <row r="224">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>3042869.33</v>
+        <v>5905118</v>
       </c>
     </row>
     <row r="227">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>2137417.32</v>
+        <v>5008003.65</v>
       </c>
     </row>
     <row r="228">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>37.41</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="230">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>10.65</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="231">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>2137417.32</v>
+        <v>5008003.65</v>
       </c>
     </row>
     <row r="236">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>-1681883.3</v>
+        <v>-2573153.93</v>
       </c>
     </row>
     <row r="237">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>227545.22</v>
+        <v>1423011.21</v>
       </c>
     </row>
     <row r="238">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>2137417.32</v>
+        <v>5008003.65</v>
       </c>
     </row>
     <row r="248">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>-1681883.3</v>
+        <v>-2573153.93</v>
       </c>
     </row>
     <row r="249">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>227545.22</v>
+        <v>1423011.21</v>
       </c>
     </row>
     <row r="250">
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>2454423.55</v>
+        <v>3312183.57</v>
       </c>
     </row>
     <row r="384">
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>34.27</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="387">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>0</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="388">
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>2180205.61</v>
+        <v>2824477.1</v>
       </c>
     </row>
     <row r="392">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>-650050.16</v>
+        <v>-926793.5600000001</v>
       </c>
     </row>
     <row r="393">
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>746305.74</v>
+        <v>1113833.83</v>
       </c>
     </row>
     <row r="394">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>77668.92</v>
+        <v>112668.92</v>
       </c>
     </row>
     <row r="395">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>-50484.8</v>
+        <v>-73234.8</v>
       </c>
     </row>
     <row r="396">
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>27184.12</v>
+        <v>39434.12</v>
       </c>
     </row>
     <row r="397">
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>30000</v>
+        <v>208488.53</v>
       </c>
     </row>
     <row r="401">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>-18900</v>
+        <v>-131347.77</v>
       </c>
     </row>
     <row r="402">
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>11100</v>
+        <v>77140.75999999999</v>
       </c>
     </row>
     <row r="403">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>2454423.55</v>
+        <v>3312183.57</v>
       </c>
     </row>
     <row r="404">
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>-829357.3100000001</v>
+        <v>-1241298.49</v>
       </c>
     </row>
     <row r="405">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>841216.53</v>
+        <v>1287035.37</v>
       </c>
     </row>
     <row r="406">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>19120.07</v>
+        <v>17429.85</v>
       </c>
     </row>
     <row r="407">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>0.5311</v>
+        <v>0.4842</v>
       </c>
     </row>
     <row r="408">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>5024268.13</v>
+        <v>5024268.01</v>
       </c>
     </row>
     <row r="409">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -10620,7 +10620,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>4114791.7</v>
+        <v>4172319.52</v>
       </c>
     </row>
     <row r="410">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>34.61</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="413">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>4114791.7</v>
+        <v>4172319.52</v>
       </c>
     </row>
     <row r="418">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>-2590732.31</v>
+        <v>-2629492.31</v>
       </c>
     </row>
     <row r="419">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>1424309.39</v>
+        <v>1443077.21</v>
       </c>
     </row>
     <row r="420">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>4114791.7</v>
+        <v>4172319.52</v>
       </c>
     </row>
     <row r="430">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>-2590732.31</v>
+        <v>-2629492.31</v>
       </c>
     </row>
     <row r="431">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AE_GM</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>1424309.39</v>
+        <v>1443077.21</v>
       </c>
     </row>
     <row r="432">
@@ -11270,7 +11270,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>15955307.69</v>
+        <v>17705307.01</v>
       </c>
     </row>
     <row r="436">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>0.5349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>3574499.98</v>
+        <v>3651164.47</v>
       </c>
     </row>
     <row r="440">
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>0.8173</v>
+        <v>0.8242</v>
       </c>
     </row>
     <row r="441">
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>0</v>
+        <v>942.91</v>
       </c>
     </row>
     <row r="466">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="467">
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>27.1</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="471">
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>41.89</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="498">
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>-2145446.18</v>
+        <v>-2133653.73</v>
       </c>
     </row>
     <row r="504">
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>1558450.5</v>
+        <v>1552100.72</v>
       </c>
     </row>
     <row r="505">
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>-2329721.18</v>
+        <v>-2317928.73</v>
       </c>
     </row>
     <row r="516">
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>1666675.5</v>
+        <v>1660325.72</v>
       </c>
     </row>
     <row r="517">
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="E524" s="2" t="n">
-        <v>4665135.85</v>
+        <v>4635362.91</v>
       </c>
     </row>
     <row r="525">
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="E525" s="2" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="526">
@@ -13545,7 +13545,7 @@
         </is>
       </c>
       <c r="E526" s="2" t="n">
-        <v>39.75</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="527">
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="E536" s="2" t="n">
-        <v>426454.36</v>
+        <v>36986.16</v>
       </c>
     </row>
     <row r="537">
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="E537" s="2" t="n">
-        <v>-288647.12</v>
+        <v>-35492.79</v>
       </c>
     </row>
     <row r="538">
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="E538" s="2" t="n">
-        <v>137807.24</v>
+        <v>1493.37</v>
       </c>
     </row>
     <row r="539">
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="E542" s="2" t="n">
-        <v>13396161.82</v>
+        <v>13006693.62</v>
       </c>
     </row>
     <row r="543">
@@ -13970,7 +13970,7 @@
         </is>
       </c>
       <c r="E543" s="2" t="n">
-        <v>-8071633.06</v>
+        <v>-7818478.73</v>
       </c>
     </row>
     <row r="544">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="E544" s="2" t="n">
-        <v>5324528.76</v>
+        <v>5188214.89</v>
       </c>
     </row>
     <row r="545">
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E602" s="2" t="n">
-        <v>0</v>
+        <v>405.77</v>
       </c>
     </row>
     <row r="603">
@@ -15470,7 +15470,7 @@
         </is>
       </c>
       <c r="E603" s="2" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="604">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="E635" s="2" t="n">
-        <v>5814009.63</v>
+        <v>5897429.1</v>
       </c>
     </row>
     <row r="636">
@@ -16295,7 +16295,7 @@
         </is>
       </c>
       <c r="E636" s="2" t="n">
-        <v>0.7977</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="637">
@@ -16320,7 +16320,7 @@
         </is>
       </c>
       <c r="E637" s="2" t="n">
-        <v>38.65</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="638">
@@ -16420,7 +16420,7 @@
         </is>
       </c>
       <c r="E641" s="2" t="n">
-        <v>16026575.21</v>
+        <v>16008432.98</v>
       </c>
     </row>
     <row r="642">
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="E642" s="2" t="n">
-        <v>-9470632.619999999</v>
+        <v>-9458840.17</v>
       </c>
     </row>
     <row r="643">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="E643" s="2" t="n">
-        <v>6555942.59</v>
+        <v>6549592.81</v>
       </c>
     </row>
     <row r="644">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="E647" s="2" t="n">
-        <v>387515.97</v>
+        <v>300331.34</v>
       </c>
     </row>
     <row r="648">
@@ -16595,7 +16595,7 @@
         </is>
       </c>
       <c r="E648" s="2" t="n">
-        <v>-251885.38</v>
+        <v>-195215.37</v>
       </c>
     </row>
     <row r="649">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E649" s="2" t="n">
-        <v>135630.59</v>
+        <v>105115.97</v>
       </c>
     </row>
     <row r="650">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="E653" s="2" t="n">
-        <v>17240011.13</v>
+        <v>17134684.27</v>
       </c>
     </row>
     <row r="654">
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="E654" s="2" t="n">
-        <v>-10577404.62</v>
+        <v>-10508942.16</v>
       </c>
     </row>
     <row r="655">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="E655" s="2" t="n">
-        <v>6662606.51</v>
+        <v>6625742.109999999</v>
       </c>
     </row>
     <row r="656">
